--- a/AAII_Financials/Yearly/HCM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HCM_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>HCM</t>
   </si>
@@ -656,148 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>838000</v>
+      </c>
+      <c r="E8" s="3">
         <v>426400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>356100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>228000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>204900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>214100</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>384400</v>
+      </c>
+      <c r="E9" s="3">
         <v>311100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>258200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>188500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>160200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>143900</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>453600</v>
+      </c>
+      <c r="E10" s="3">
         <v>115300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>97900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>39500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>44700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>70200</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,38 +822,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E12" s="3">
         <v>386900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>299100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>174800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>138200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>114200</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,39 +885,45 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>5800</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -929,9 +951,12 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,68 +966,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>825400</v>
+      </c>
+      <c r="E17" s="3">
         <v>834100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>563100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>424600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>351300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>306800</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-407700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-207000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-196700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-146400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-92600</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,88 +1047,95 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>93800</v>
+      </c>
+      <c r="E20" s="3">
         <v>47700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>52500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>86800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>47000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>26300</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>114600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-351400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-147300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-103800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-94400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-62700</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>800</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>800</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1000</v>
       </c>
       <c r="H22" s="3">
         <v>1000</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>1000</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1104,69 +1143,78 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>105600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-360700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-155100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-110700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-100400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-67300</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,69 +1242,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>101100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-360400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-167000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-115500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-103700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-71300</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-360800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-194600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-125700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-106000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-74800</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,69 +1440,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-93800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-47700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-52500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-86800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-47000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-26300</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-360800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-194600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-125700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-106000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-74800</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,74 +1539,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-360800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-194600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-125700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-106000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-74800</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,26 +1643,27 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>283600</v>
+      </c>
+      <c r="E41" s="3">
         <v>313300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>377500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>235600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>121200</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1587,27 +1673,30 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>602700</v>
+      </c>
+      <c r="E42" s="3">
         <v>318900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>635400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>201400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>96900</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1617,27 +1706,30 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>153100</v>
+      </c>
+      <c r="E43" s="3">
         <v>128700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>149200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>66900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>79000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1647,27 +1739,30 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E44" s="3">
         <v>56700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>35800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>19800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16200</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1677,27 +1772,30 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E45" s="3">
         <v>22300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3800</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1707,27 +1805,30 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1096800</v>
+      </c>
+      <c r="E46" s="3">
         <v>839900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1212100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>530700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>317000</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,27 +1838,30 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E47" s="3">
         <v>73800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>76500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>139500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>115100</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1767,27 +1871,30 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>104400</v>
+      </c>
+      <c r="E48" s="3">
         <v>84700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>53200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>27500</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1797,9 +1904,12 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1812,12 +1922,12 @@
       <c r="F49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3">
         <v>3400</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1827,9 +1937,12 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,27 +2003,30 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E52" s="3">
         <v>31100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>31000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -1917,9 +2036,12 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,27 +2069,30 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1279800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1029400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1372700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>724100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>465100</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1977,9 +2102,12 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,26 +2135,27 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E57" s="3">
         <v>71100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>41200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>24000</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2035,27 +2165,30 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>35100</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>26900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3200</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2065,27 +2198,30 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>331600</v>
+      </c>
+      <c r="E59" s="3">
         <v>282800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>243600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>124000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>85900</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,27 +2231,30 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>403000</v>
+      </c>
+      <c r="E60" s="3">
         <v>353900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>311700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>158400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>113100</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2125,27 +2264,30 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E61" s="3">
         <v>23300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>32900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>29900</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2155,27 +2297,30 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E62" s="3">
         <v>15400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9300</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2185,9 +2330,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,27 +2429,30 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>549200</v>
+      </c>
+      <c r="E66" s="3">
         <v>419100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>385800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>240000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>177100</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2305,9 +2462,12 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,27 +2609,30 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-870900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-971500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-610300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-415600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-289700</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,9 +2642,12 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,27 +2741,30 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>730500</v>
+      </c>
+      <c r="E76" s="3">
         <v>610400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>986900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>484100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>288000</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,9 +2774,12 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,74 +2807,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-360800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-194600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-125700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-106000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-74800</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,38 +2896,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E83" s="3">
         <v>8700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3600</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,39 +3091,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>219300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-268600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-204200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-62100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-80900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-32800</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,38 +3142,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6400</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,39 +3238,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-291100</v>
+      </c>
+      <c r="E94" s="3">
         <v>296600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-306300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-125400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>119000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>43800</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,8 +3289,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3086,9 +3319,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,97 +3418,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-82800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>650000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>296400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8200</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-64300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>141900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>114500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>35100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>800</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HCM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HCM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>HCM</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -699,8 +699,8 @@
       <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="J7" s="2">
+        <v>43100</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -732,8 +732,8 @@
       <c r="I8" s="3">
         <v>214100</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+      <c r="J8" s="3">
+        <v>241200</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -748,25 +748,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>384400</v>
+        <v>686400</v>
       </c>
       <c r="E9" s="3">
-        <v>311100</v>
+        <v>698000</v>
       </c>
       <c r="F9" s="3">
-        <v>258200</v>
+        <v>557300</v>
       </c>
       <c r="G9" s="3">
-        <v>188500</v>
+        <v>363300</v>
       </c>
       <c r="H9" s="3">
-        <v>160200</v>
+        <v>298300</v>
       </c>
       <c r="I9" s="3">
-        <v>143900</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>258100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>251300</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -781,25 +781,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>453600</v>
+        <v>151600</v>
       </c>
       <c r="E10" s="3">
-        <v>115300</v>
+        <v>-271600</v>
       </c>
       <c r="F10" s="3">
-        <v>97900</v>
+        <v>-201200</v>
       </c>
       <c r="G10" s="3">
-        <v>39500</v>
+        <v>-135300</v>
       </c>
       <c r="H10" s="3">
-        <v>44700</v>
+        <v>-93500</v>
       </c>
       <c r="I10" s="3">
-        <v>70200</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>-44000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-10100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -829,25 +829,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>302000</v>
+        <v>303100</v>
       </c>
       <c r="E12" s="3">
-        <v>386900</v>
+        <v>391400</v>
       </c>
       <c r="F12" s="3">
-        <v>299100</v>
+        <v>314600</v>
       </c>
       <c r="G12" s="3">
         <v>174800</v>
       </c>
       <c r="H12" s="3">
-        <v>138200</v>
+        <v>144300</v>
       </c>
       <c r="I12" s="3">
-        <v>114200</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+        <v>115600</v>
+      </c>
+      <c r="J12" s="3">
+        <v>76400</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -900,8 +900,8 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3">
+        <v>-121300</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -928,25 +928,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -973,13 +973,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>825400</v>
+        <v>819600</v>
       </c>
       <c r="E17" s="3">
         <v>834100</v>
       </c>
       <c r="F17" s="3">
-        <v>563100</v>
+        <v>684400</v>
       </c>
       <c r="G17" s="3">
         <v>424600</v>
@@ -990,8 +990,8 @@
       <c r="I17" s="3">
         <v>306800</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+      <c r="J17" s="3">
+        <v>294600</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1006,13 +1006,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>12600</v>
+        <v>18400</v>
       </c>
       <c r="E18" s="3">
         <v>-407700</v>
       </c>
       <c r="F18" s="3">
-        <v>-207000</v>
+        <v>-328300</v>
       </c>
       <c r="G18" s="3">
         <v>-196700</v>
@@ -1023,8 +1023,8 @@
       <c r="I18" s="3">
         <v>-92600</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+      <c r="J18" s="3">
+        <v>-53400</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1054,25 +1054,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>93800</v>
+        <v>-57600</v>
       </c>
       <c r="E20" s="3">
-        <v>47700</v>
+        <v>-38100</v>
       </c>
       <c r="F20" s="3">
-        <v>52500</v>
+        <v>-50400</v>
       </c>
       <c r="G20" s="3">
-        <v>86800</v>
+        <v>-83500</v>
       </c>
       <c r="H20" s="3">
-        <v>47000</v>
+        <v>-42100</v>
       </c>
       <c r="I20" s="3">
-        <v>26300</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>-20400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-33800</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1087,25 +1087,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>114600</v>
+        <v>84200</v>
       </c>
       <c r="E21" s="3">
-        <v>-351400</v>
+        <v>-361000</v>
       </c>
       <c r="F21" s="3">
-        <v>-147300</v>
+        <v>-270700</v>
       </c>
       <c r="G21" s="3">
-        <v>-103800</v>
+        <v>-107100</v>
       </c>
       <c r="H21" s="3">
-        <v>-94400</v>
+        <v>-99400</v>
       </c>
       <c r="I21" s="3">
-        <v>-62700</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-68700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-17100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1137,8 +1137,8 @@
       <c r="I22" s="3">
         <v>1000</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>1500</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1170,8 +1170,8 @@
       <c r="I23" s="3">
         <v>-67300</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+      <c r="J23" s="3">
+        <v>-19900</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1203,8 +1203,8 @@
       <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>3100</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1269,8 +1269,8 @@
       <c r="I26" s="3">
         <v>-71300</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+      <c r="J26" s="3">
+        <v>-23000</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1291,7 +1291,7 @@
         <v>-360800</v>
       </c>
       <c r="F27" s="3">
-        <v>-194600</v>
+        <v>-194700</v>
       </c>
       <c r="G27" s="3">
         <v>-125700</v>
@@ -1302,8 +1302,8 @@
       <c r="I27" s="3">
         <v>-74800</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+      <c r="J27" s="3">
+        <v>-26700</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1450,25 +1450,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-93800</v>
+        <v>57600</v>
       </c>
       <c r="E32" s="3">
-        <v>-47700</v>
+        <v>38100</v>
       </c>
       <c r="F32" s="3">
-        <v>-52500</v>
+        <v>50400</v>
       </c>
       <c r="G32" s="3">
-        <v>-86800</v>
+        <v>83500</v>
       </c>
       <c r="H32" s="3">
-        <v>-47000</v>
+        <v>42100</v>
       </c>
       <c r="I32" s="3">
-        <v>-26300</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>20400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>33800</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1500,8 +1500,8 @@
       <c r="I33" s="3">
         <v>-74800</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+      <c r="J33" s="3">
+        <v>-26700</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1566,8 +1566,8 @@
       <c r="I35" s="3">
         <v>-74800</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+      <c r="J35" s="3">
+        <v>-26700</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1604,8 +1604,8 @@
       <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="J38" s="2">
+        <v>43100</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1664,11 +1664,11 @@
       <c r="H41" s="3">
         <v>121200</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="I41" s="3">
+        <v>86000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>85300</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1683,25 +1683,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>602700</v>
+        <v>605400</v>
       </c>
       <c r="E42" s="3">
-        <v>318900</v>
+        <v>320100</v>
       </c>
       <c r="F42" s="3">
-        <v>635400</v>
+        <v>636900</v>
       </c>
       <c r="G42" s="3">
-        <v>201400</v>
+        <v>203400</v>
       </c>
       <c r="H42" s="3">
-        <v>96900</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>98500</v>
+      </c>
+      <c r="I42" s="3">
+        <v>216700</v>
+      </c>
+      <c r="J42" s="3">
+        <v>273000</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1716,25 +1716,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>153100</v>
+        <v>150500</v>
       </c>
       <c r="E43" s="3">
-        <v>128700</v>
+        <v>127500</v>
       </c>
       <c r="F43" s="3">
-        <v>149200</v>
+        <v>147700</v>
       </c>
       <c r="G43" s="3">
-        <v>66900</v>
+        <v>64000</v>
       </c>
       <c r="H43" s="3">
-        <v>79000</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>77300</v>
+      </c>
+      <c r="I43" s="3">
+        <v>51200</v>
+      </c>
+      <c r="J43" s="3">
+        <v>62100</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1763,11 +1763,11 @@
       <c r="H44" s="3">
         <v>16200</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+      <c r="I44" s="3">
+        <v>12300</v>
+      </c>
+      <c r="J44" s="3">
+        <v>11800</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1781,20 +1781,20 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>7100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>22300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>14100</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3">
-        <v>7000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3800</v>
+        <v>900</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1829,11 +1829,11 @@
       <c r="H46" s="3">
         <v>317000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="I46" s="3">
+        <v>370500</v>
+      </c>
+      <c r="J46" s="3">
+        <v>432200</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1860,13 +1860,13 @@
         <v>139500</v>
       </c>
       <c r="H47" s="3">
-        <v>115100</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>98900</v>
+      </c>
+      <c r="I47" s="3">
+        <v>138300</v>
+      </c>
+      <c r="J47" s="3">
+        <v>144200</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1893,13 +1893,13 @@
         <v>32200</v>
       </c>
       <c r="H48" s="3">
-        <v>27500</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>26400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>16600</v>
+      </c>
+      <c r="J48" s="3">
+        <v>14200</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1913,26 +1913,26 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>3500</v>
       </c>
       <c r="H49" s="3">
         <v>3400</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J49" s="3">
+        <v>3700</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2013,25 +2013,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>30100</v>
+        <v>14700</v>
       </c>
       <c r="E52" s="3">
-        <v>31100</v>
+        <v>15700</v>
       </c>
       <c r="F52" s="3">
-        <v>31000</v>
+        <v>21600</v>
       </c>
       <c r="G52" s="3">
-        <v>21700</v>
+        <v>15500</v>
       </c>
       <c r="H52" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>18400</v>
+      </c>
+      <c r="I52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>2900</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2093,11 +2093,11 @@
       <c r="H54" s="3">
         <v>465100</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+      <c r="I54" s="3">
+        <v>532100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>597900</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2156,11 +2156,11 @@
       <c r="H57" s="3">
         <v>24000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="I57" s="3">
+        <v>25600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>24400</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2178,22 +2178,22 @@
         <v>35100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="F58" s="3">
-        <v>26900</v>
+        <v>31800</v>
       </c>
       <c r="G58" s="3">
         <v>2800</v>
       </c>
       <c r="H58" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>3600</v>
+      </c>
+      <c r="I58" s="3">
+        <v>400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>32000</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2208,25 +2208,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>331600</v>
+        <v>100700</v>
       </c>
       <c r="E59" s="3">
-        <v>282800</v>
+        <v>54400</v>
       </c>
       <c r="F59" s="3">
-        <v>243600</v>
+        <v>56500</v>
       </c>
       <c r="G59" s="3">
-        <v>124000</v>
+        <v>13300</v>
       </c>
       <c r="H59" s="3">
-        <v>85900</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>12000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>11000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>8900</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2255,11 +2255,11 @@
       <c r="H60" s="3">
         <v>113100</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="I60" s="3">
+        <v>85500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>104600</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2283,16 +2283,16 @@
         <v>7200</v>
       </c>
       <c r="G61" s="3">
-        <v>32900</v>
+        <v>33500</v>
       </c>
       <c r="H61" s="3">
-        <v>29900</v>
+        <v>30400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>27300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2307,25 +2307,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>82300</v>
+        <v>11300</v>
       </c>
       <c r="E62" s="3">
-        <v>15400</v>
+        <v>12500</v>
       </c>
       <c r="F62" s="3">
-        <v>14300</v>
+        <v>10700</v>
       </c>
       <c r="G62" s="3">
-        <v>13800</v>
+        <v>7700</v>
       </c>
       <c r="H62" s="3">
-        <v>9300</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>5400</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J62" s="3">
+        <v>500</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2439,25 +2439,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>549200</v>
+        <v>536400</v>
       </c>
       <c r="E66" s="3">
-        <v>419100</v>
+        <v>392600</v>
       </c>
       <c r="F66" s="3">
-        <v>385800</v>
+        <v>333100</v>
       </c>
       <c r="G66" s="3">
-        <v>240000</v>
+        <v>205200</v>
       </c>
       <c r="H66" s="3">
-        <v>177100</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>152200</v>
+      </c>
+      <c r="I66" s="3">
+        <v>119900</v>
+      </c>
+      <c r="J66" s="3">
+        <v>113000</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2633,11 +2633,11 @@
       <c r="H72" s="3">
         <v>-289700</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="I72" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-107100</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2765,11 +2765,11 @@
       <c r="H76" s="3">
         <v>288000</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="I76" s="3">
+        <v>389000</v>
+      </c>
+      <c r="J76" s="3">
+        <v>461700</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2839,8 +2839,8 @@
       <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="J80" s="2">
+        <v>43100</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2872,8 +2872,8 @@
       <c r="I81" s="3">
         <v>-74800</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+      <c r="J81" s="3">
+        <v>-26700</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2918,10 +2918,10 @@
         <v>4900</v>
       </c>
       <c r="I83" s="3">
-        <v>3600</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>3500</v>
+      </c>
+      <c r="J83" s="3">
+        <v>2500</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3118,8 +3118,8 @@
       <c r="I89" s="3">
         <v>-32800</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+      <c r="J89" s="3">
+        <v>-8900</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3155,10 +3155,10 @@
         <v>-36700</v>
       </c>
       <c r="F91" s="3">
-        <v>-16800</v>
+        <v>-16400</v>
       </c>
       <c r="G91" s="3">
-        <v>-19600</v>
+        <v>-7900</v>
       </c>
       <c r="H91" s="3">
         <v>-8600</v>
@@ -3166,8 +3166,8 @@
       <c r="I91" s="3">
         <v>-6400</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+      <c r="J91" s="3">
+        <v>-5000</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3265,8 +3265,8 @@
       <c r="I94" s="3">
         <v>43800</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3">
+        <v>-260800</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3445,8 +3445,8 @@
       <c r="I100" s="3">
         <v>-8200</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="J100" s="3">
+        <v>273200</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3478,8 +3478,8 @@
       <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>2400</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3511,8 +3511,8 @@
       <c r="I102" s="3">
         <v>800</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="J102" s="3">
+        <v>5800</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/HCM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HCM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>HCM</t>
   </si>
@@ -656,160 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>630200</v>
+      </c>
+      <c r="E8" s="3">
         <v>838000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>426400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>356100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>228000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>204900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>214100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>241200</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E9" s="3">
         <v>686400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>698000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>557300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>363300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>298300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>258100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>251300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E10" s="3">
         <v>151600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-271600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-201200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-135300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-93500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-44000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-10100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,41 +835,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>213400</v>
+      </c>
+      <c r="E12" s="3">
         <v>303100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>391400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>314600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>174800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>144300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>115600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>76400</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,24 +904,27 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E14" s="3">
         <v>5800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>-121300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -915,48 +934,54 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E15" s="3">
         <v>8200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +992,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>673900</v>
+      </c>
+      <c r="E17" s="3">
         <v>819600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>834100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>684400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>424600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>351300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>306800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>294600</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="E18" s="3">
         <v>18400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-407700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-328300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-196700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-146400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-92600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-53400</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,173 +1080,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-56700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-57600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-38100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-50400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-83500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-42100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-20400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-33800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E21" s="3">
         <v>84200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-361000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-270700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-107100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-99400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-68700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E22" s="3">
         <v>800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>800</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1000</v>
       </c>
       <c r="I22" s="3">
         <v>1000</v>
       </c>
       <c r="J22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K22" s="3">
         <v>1500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E23" s="3">
         <v>105600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-360700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-155100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-110700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-67300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19900</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E24" s="3">
         <v>4500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1293,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E26" s="3">
         <v>101100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-360400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-167000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-115500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-103700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-71300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23000</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E27" s="3">
         <v>100800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-360800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-194700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-125700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-106000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-74800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26700</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1509,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E32" s="3">
         <v>57600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>38100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>50400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>83500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>42100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>20400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>33800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E33" s="3">
         <v>100800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-360800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-194600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-125700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-106000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-74800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26700</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1617,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E35" s="3">
         <v>100800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-360800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-194600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-125700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-106000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-74800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26700</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,140 +1729,153 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E41" s="3">
         <v>283600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>313300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>377500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>235600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>121200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>86000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>85300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>684800</v>
+      </c>
+      <c r="E42" s="3">
         <v>605400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>320100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>636900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>203400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>98500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>216700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>273000</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>169500</v>
+      </c>
+      <c r="E43" s="3">
         <v>150500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>147700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>64000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>77300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>51200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>62100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E44" s="3">
         <v>50300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>56700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>35800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>19800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11800</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1790,12 +1888,12 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,108 +1906,120 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1066600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1096800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>839900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1212100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>530700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>317000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>370500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>432200</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E47" s="3">
         <v>48400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>73800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>76500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>139500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>98900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>138300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>144200</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E48" s="3">
         <v>104400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>84700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>53200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1923,26 +2033,29 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>3500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3700</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,42 +2122,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E52" s="3">
         <v>14700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2900</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1274200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1279800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1029400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1372700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>724100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>465100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>532100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>597900</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,206 +2265,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E57" s="3">
         <v>36300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>71100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>25600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E58" s="3">
         <v>35100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>31800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>32000</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100700</v>
+        <v>93200</v>
       </c>
       <c r="E59" s="3">
+        <v>98600</v>
+      </c>
+      <c r="F59" s="3">
         <v>54400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>56500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8900</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>376600</v>
+      </c>
+      <c r="E60" s="3">
         <v>403000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>353900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>311700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>158400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>113100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>85500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>104600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E61" s="3">
         <v>51000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>23300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>33500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>30400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>27300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E62" s="3">
         <v>11300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2586,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>502300</v>
+      </c>
+      <c r="E66" s="3">
         <v>536400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>392600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>333100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>205200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>152200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>119900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>113000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2782,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-833200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-870900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-971500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-610300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-415600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-289700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-183000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-107100</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>759900</v>
+      </c>
+      <c r="E76" s="3">
         <v>730500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>610400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>986900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>484100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>288000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>389000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>461700</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2998,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E81" s="3">
         <v>100800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-360800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-194600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-125700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-106000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-74800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26700</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3094,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E83" s="3">
         <v>8200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3307,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
         <v>219300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-268600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-204200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-62100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-80900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-32800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8900</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3362,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-32600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-36700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5000</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3467,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-96100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-291100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>296600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-306300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-125400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>119000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>43800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-260800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,8 +3522,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,106 +3663,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E100" s="3">
         <v>48700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-82800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>650000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>296400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>273200</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2400</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-129600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-29700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-64300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>141900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>114500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>35100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5800</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HCM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HCM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>HCM</t>
   </si>
@@ -656,172 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>548500</v>
+      </c>
+      <c r="E8" s="3">
         <v>630200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>838000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>426400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>356100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>228000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>204900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>214100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>241200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>484600</v>
+      </c>
+      <c r="E9" s="3">
         <v>561000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>686400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>698000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>557300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>363300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>298300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>258100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>251300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E10" s="3">
         <v>69200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>151600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-271600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-201200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-135300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-93500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-44000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-10100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,44 +848,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>154700</v>
+      </c>
+      <c r="E12" s="3">
         <v>213400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>303100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>391400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>314600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>174800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>144300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>115600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>76400</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,27 +923,30 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-478800</v>
+      </c>
+      <c r="E14" s="3">
         <v>4800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>-121300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -937,51 +956,57 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E15" s="3">
         <v>12300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,80 +1018,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>587700</v>
+      </c>
+      <c r="E17" s="3">
         <v>673900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>819600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>834100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>684400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>424600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>351300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>306800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>294600</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-39200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-43700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-407700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-328300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-196700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-146400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-92600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-53400</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,80 +1113,87 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-56700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-57600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-38100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-50400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-83500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-42100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-20400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-33800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E21" s="3">
         <v>25300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>84200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-361000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-270700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-107100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-99400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-68700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1162,107 +1201,116 @@
         <v>2900</v>
       </c>
       <c r="E22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F22" s="3">
         <v>800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1000</v>
       </c>
       <c r="J22" s="3">
         <v>1000</v>
       </c>
       <c r="K22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L22" s="3">
         <v>1500</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>521300</v>
+      </c>
+      <c r="E23" s="3">
         <v>45400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>105600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-360700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-155100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-110700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-100400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-67300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>63600</v>
+      </c>
+      <c r="E24" s="3">
         <v>7200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,81 +1344,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>457700</v>
+      </c>
+      <c r="E26" s="3">
         <v>38200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>101100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-360400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-167000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-115500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-103700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-71300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-23000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>456900</v>
+      </c>
+      <c r="E27" s="3">
         <v>37700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>100800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-360800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-194700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-125700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-106000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-74800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26700</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,9 +1461,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1440,9 +1500,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,81 +1578,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E32" s="3">
         <v>56700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>57600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>38100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>50400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>83500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>42100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>20400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>33800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>456900</v>
+      </c>
+      <c r="E33" s="3">
         <v>37700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>100800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-360800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-194600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-125700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-106000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-74800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26700</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,86 +1695,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>456900</v>
+      </c>
+      <c r="E35" s="3">
         <v>37700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>100800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-360800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-194600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-125700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-106000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-74800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26700</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,152 +1815,165 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71300</v>
+      </c>
+      <c r="E41" s="3">
         <v>154000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>283600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>313300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>377500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>235600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>121200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>86000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>85300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>684800</v>
+        <v>1297600</v>
       </c>
       <c r="E42" s="3">
+        <v>684000</v>
+      </c>
+      <c r="F42" s="3">
         <v>605400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>320100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>636900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>203400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>98500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>216700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>273000</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>169500</v>
+        <v>149000</v>
       </c>
       <c r="E43" s="3">
+        <v>170300</v>
+      </c>
+      <c r="F43" s="3">
         <v>150500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>127500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>147700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>64000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>77300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>51200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>62100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E44" s="3">
         <v>50400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>50300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>56700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>35800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>19800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>16200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11800</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1891,12 +1989,12 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1909,125 +2007,137 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1567300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1066600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1096800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>839900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1212100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>530700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>317000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>370500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>432200</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E47" s="3">
         <v>82800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>48400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>73800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>76500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>139500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>98900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>138300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>144200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E48" s="3">
         <v>97000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>104400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>84700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>53200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>16600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -2036,26 +2146,29 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>3500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3700</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,45 +2241,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>15400</v>
+        <v>61500</v>
       </c>
       <c r="E52" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F52" s="3">
         <v>14700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2900</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,45 +2319,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1753100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1274200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1279800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1029400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1372700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>724100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>465100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>532100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>597900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,224 +2395,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E57" s="3">
         <v>42500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>71100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>25600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E58" s="3">
         <v>26300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>35100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>31800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>32000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>67400</v>
+      </c>
+      <c r="E59" s="3">
         <v>93200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>98600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>54400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>56500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>315800</v>
+      </c>
+      <c r="E60" s="3">
         <v>376600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>403000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>353900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>311700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>158400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>113100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>85500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>104600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E61" s="3">
         <v>63500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>51000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>33500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>30400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>27300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>95600</v>
+      </c>
+      <c r="E62" s="3">
         <v>10800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>12500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,45 +2743,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>501800</v>
+      </c>
+      <c r="E66" s="3">
         <v>502300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>536400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>392600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>333100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>205200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>152200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>119900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>113000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,45 +2955,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-378600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-833200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-870900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-971500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-610300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-415600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-289700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-183000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-107100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,45 +3111,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1237900</v>
+      </c>
+      <c r="E76" s="3">
         <v>759900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>730500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>610400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>986900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>484100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>288000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>389000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>461700</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,86 +3189,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>456900</v>
+      </c>
+      <c r="E81" s="3">
         <v>37700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>100800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-360800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-194600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-125700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-106000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-74800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26700</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,44 +3292,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E83" s="3">
         <v>12300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,45 +3523,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-64700</v>
+      </c>
+      <c r="E89" s="3">
         <v>500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>219300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-268600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-204200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-62100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-80900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-32800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8900</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,44 +3582,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-32600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,45 +3696,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-96100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-291100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>296600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-306300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-125400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>119000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>43800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-260800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,8 +3755,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3558,9 +3791,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,115 +3908,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-30700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>48700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-82800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>650000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>296400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>273200</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2400</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-82600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-129600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-29700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-64300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>141900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>114500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>35100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5800</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
